--- a/Classification/baseline/results/uncertainty_results/conformal_reports_all_models.xlsx
+++ b/Classification/baseline/results/uncertainty_results/conformal_reports_all_models.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="104">
   <si>
     <t>model_name</t>
   </si>
@@ -151,22 +151,19 @@
     <t>timestamp_utc</t>
   </si>
   <si>
-    <t>/content/drive/My Drive/Classification/data/data.csv</t>
-  </si>
-  <si>
-    <t>/content/drive/My Drive/Classification/data/ref.csv</t>
-  </si>
-  <si>
-    <t>/content/drive/My Drive/Classification/baseline/models</t>
-  </si>
-  <si>
-    <t>/content/drive/My Drive/Classification/baseline/results/uncertainty_results</t>
-  </si>
-  <si>
-    <t>/content/drive/My Drive/Classification/baseline/results</t>
-  </si>
-  <si>
-    <t>2026-05-27T17:36:35.339062+00:00</t>
+    <t>/kaggle/input/datasets/daneshselwal/dias-6-bands-data/k001.csv</t>
+  </si>
+  <si>
+    <t>/kaggle/input/datasets/daneshselwal/dias-6-bands-data/k002.csv</t>
+  </si>
+  <si>
+    <t>/kaggle/input</t>
+  </si>
+  <si>
+    <t>/kaggle/working/Classification/baseline/results/uncertainty_results</t>
+  </si>
+  <si>
+    <t>2026-10-11T10:18:59.049575+00:00</t>
   </si>
   <si>
     <t>SplitConformal - AlexNet</t>
@@ -2934,28 +2931,28 @@
         <v>0.95</v>
       </c>
       <c r="D2">
-        <v>0.9642691415313225</v>
+        <v>0.9647331786542923</v>
       </c>
       <c r="E2">
-        <v>0.9642691415313225</v>
+        <v>0.9647331786542923</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>0.9642691415313225</v>
+        <v>0.9647331786542923</v>
       </c>
       <c r="H2">
-        <v>0.0357308584686775</v>
+        <v>0.03526682134570765</v>
       </c>
       <c r="I2">
-        <v>2.050202063000143</v>
+        <v>1.519001585000012</v>
       </c>
       <c r="J2">
         <v>0.05</v>
       </c>
       <c r="M2">
-        <v>0.9595146470000567</v>
+        <v>0.968021548786501</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2969,28 +2966,28 @@
         <v>0.95</v>
       </c>
       <c r="D3">
-        <v>0.9610208816705337</v>
+        <v>0.9619489559164733</v>
       </c>
       <c r="E3">
-        <v>0.9614849187935035</v>
+        <v>0.9624129930394432</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>0.9614849187935035</v>
+        <v>0.9624129930394432</v>
       </c>
       <c r="H3">
-        <v>0.03851508120649652</v>
+        <v>0.03758700696055684</v>
       </c>
       <c r="I3">
-        <v>1.587323905000176</v>
+        <v>1.50927251600001</v>
       </c>
       <c r="J3">
         <v>0.05</v>
       </c>
       <c r="M3">
-        <v>0.9605619388469139</v>
+        <v>0.9709575072012449</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3004,7 +3001,7 @@
         <v>0.95</v>
       </c>
       <c r="D4">
-        <v>0.954524361948956</v>
+        <v>0.9559164733178654</v>
       </c>
       <c r="E4">
         <v>0.9577726218097448</v>
@@ -3019,13 +3016,13 @@
         <v>0.04222737819025522</v>
       </c>
       <c r="I4">
-        <v>1.594293684000149</v>
+        <v>1.56471768900002</v>
       </c>
       <c r="J4">
         <v>0.05</v>
       </c>
       <c r="M4">
-        <v>0.9602821140459792</v>
+        <v>0.9610168565602223</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -3039,22 +3036,22 @@
         <v>0.95</v>
       </c>
       <c r="D5">
-        <v>0.9568445475638051</v>
+        <v>0.9651972157772621</v>
       </c>
       <c r="E5">
-        <v>0.9568445475638051</v>
+        <v>0.9651972157772621</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>0.9568445475638051</v>
+        <v>0.9651972157772621</v>
       </c>
       <c r="H5">
-        <v>0.0431554524361949</v>
+        <v>0.03480278422273782</v>
       </c>
       <c r="I5">
-        <v>2.497895874999813</v>
+        <v>2.407274647999998</v>
       </c>
       <c r="J5">
         <v>0.05</v>
@@ -3063,7 +3060,7 @@
         <v>4</v>
       </c>
       <c r="M5">
-        <v>0.9474320355358241</v>
+        <v>0.9546374488073269</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3077,22 +3074,22 @@
         <v>0.95</v>
       </c>
       <c r="D6">
-        <v>0.9503480278422274</v>
+        <v>0.9596287703016241</v>
       </c>
       <c r="E6">
-        <v>0.9503480278422274</v>
+        <v>0.9596287703016241</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6">
-        <v>0.9503480278422274</v>
+        <v>0.9596287703016241</v>
       </c>
       <c r="H6">
-        <v>0.04965197215777262</v>
+        <v>0.04037122969837587</v>
       </c>
       <c r="I6">
-        <v>6.272273327000221</v>
+        <v>4.517080029999988</v>
       </c>
       <c r="J6">
         <v>0.05</v>
@@ -3101,7 +3098,7 @@
         <v>4</v>
       </c>
       <c r="M6">
-        <v>0.9459429557019886</v>
+        <v>0.9589286748347672</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3115,22 +3112,22 @@
         <v>0.95</v>
       </c>
       <c r="D7">
-        <v>0.951276102088167</v>
+        <v>0.9535962877030162</v>
       </c>
       <c r="E7">
-        <v>0.9535962877030162</v>
+        <v>0.9554524361948956</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
-        <v>0.9535962877030162</v>
+        <v>0.9554524361948956</v>
       </c>
       <c r="H7">
-        <v>0.04640371229698376</v>
+        <v>0.04454756380510441</v>
       </c>
       <c r="I7">
-        <v>11.06494913400002</v>
+        <v>9.133538877000035</v>
       </c>
       <c r="J7">
         <v>0.05</v>
@@ -3139,7 +3136,7 @@
         <v>4</v>
       </c>
       <c r="M7">
-        <v>0.9585776484037607</v>
+        <v>0.9442845717138543</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -3168,7 +3165,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.3968220050001037</v>
+        <v>0.3762310320000211</v>
       </c>
       <c r="J8">
         <v>0.05</v>
@@ -3177,7 +3174,7 @@
         <v>0.01</v>
       </c>
       <c r="M8">
-        <v>0.9992862943912584</v>
+        <v>0.9975844963536076</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3206,7 +3203,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0.4127142659999663</v>
+        <v>0.7239199800000051</v>
       </c>
       <c r="J9">
         <v>0.05</v>
@@ -3215,7 +3212,7 @@
         <v>0.01</v>
       </c>
       <c r="M9">
-        <v>0.9974880798903145</v>
+        <v>0.9964726950317967</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -3229,7 +3226,7 @@
         <v>0.95</v>
       </c>
       <c r="D10">
-        <v>0.9925754060324826</v>
+        <v>0.9939675174013921</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -3244,7 +3241,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0.4107737730000736</v>
+        <v>0.3752910420000148</v>
       </c>
       <c r="J10">
         <v>0.05</v>
@@ -3253,7 +3250,7 @@
         <v>0.01</v>
       </c>
       <c r="M10">
-        <v>0.9899444570242417</v>
+        <v>0.9925457202024014</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -3267,28 +3264,28 @@
         <v>0.95</v>
       </c>
       <c r="D11">
-        <v>0.9670533642691416</v>
+        <v>0.9716937354988399</v>
       </c>
       <c r="E11">
-        <v>0.9670533642691416</v>
+        <v>0.9716937354988399</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11">
-        <v>0.9670533642691416</v>
+        <v>0.9716937354988399</v>
       </c>
       <c r="H11">
-        <v>0.03294663573085847</v>
+        <v>0.02830626450116009</v>
       </c>
       <c r="I11">
-        <v>1.603470881000248</v>
+        <v>1.489061632000016</v>
       </c>
       <c r="J11">
         <v>0.05</v>
       </c>
       <c r="M11">
-        <v>0.961613000054715</v>
+        <v>0.974236360209212</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -3302,28 +3299,28 @@
         <v>0.95</v>
       </c>
       <c r="D12">
+        <v>0.965661252900232</v>
+      </c>
+      <c r="E12">
         <v>0.9661252900232019</v>
       </c>
-      <c r="E12">
-        <v>0.9670533642691416</v>
-      </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12">
-        <v>0.9670533642691416</v>
+        <v>0.9661252900232019</v>
       </c>
       <c r="H12">
-        <v>0.03294663573085847</v>
+        <v>0.03387470997679815</v>
       </c>
       <c r="I12">
-        <v>1.596849406000274</v>
+        <v>1.484987718000014</v>
       </c>
       <c r="J12">
         <v>0.05</v>
       </c>
       <c r="M12">
-        <v>0.9723330633020304</v>
+        <v>0.9754523849408642</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -3337,28 +3334,28 @@
         <v>0.95</v>
       </c>
       <c r="D13">
-        <v>0.9577726218097448</v>
+        <v>0.962877030162413</v>
       </c>
       <c r="E13">
-        <v>0.9610208816705337</v>
+        <v>0.9647331786542923</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13">
-        <v>0.9610208816705337</v>
+        <v>0.9647331786542923</v>
       </c>
       <c r="H13">
-        <v>0.03897911832946636</v>
+        <v>0.03526682134570765</v>
       </c>
       <c r="I13">
-        <v>2.617920029000288</v>
+        <v>1.48396456200004</v>
       </c>
       <c r="J13">
         <v>0.05</v>
       </c>
       <c r="M13">
-        <v>0.9640907949938825</v>
+        <v>0.9697495534767266</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -3372,28 +3369,28 @@
         <v>0.95</v>
       </c>
       <c r="D14">
-        <v>0.9582366589327146</v>
+        <v>0.9577726218097448</v>
       </c>
       <c r="E14">
-        <v>0.9582366589327146</v>
+        <v>0.9577726218097448</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14">
-        <v>0.9582366589327146</v>
+        <v>0.9577726218097448</v>
       </c>
       <c r="H14">
-        <v>0.04176334106728538</v>
+        <v>0.04222737819025522</v>
       </c>
       <c r="I14">
-        <v>2.624444249999669</v>
+        <v>1.631907137999974</v>
       </c>
       <c r="J14">
         <v>0.05</v>
       </c>
       <c r="M14">
-        <v>0.9299937688165701</v>
+        <v>0.9154465450525774</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -3407,28 +3404,28 @@
         <v>0.95</v>
       </c>
       <c r="D15">
-        <v>0.9522041763341067</v>
+        <v>0.9498839907192576</v>
       </c>
       <c r="E15">
-        <v>0.9522041763341067</v>
+        <v>0.9498839907192576</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15">
-        <v>0.9522041763341067</v>
+        <v>0.9498839907192576</v>
       </c>
       <c r="H15">
-        <v>0.04779582366589327</v>
+        <v>0.05011600928074246</v>
       </c>
       <c r="I15">
-        <v>1.608272338000006</v>
+        <v>1.53999763600001</v>
       </c>
       <c r="J15">
         <v>0.05</v>
       </c>
       <c r="M15">
-        <v>0.9232578513467463</v>
+        <v>0.9226677227224513</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -3442,28 +3439,28 @@
         <v>0.95</v>
       </c>
       <c r="D16">
-        <v>0.9475638051044084</v>
+        <v>0.9540603248259861</v>
       </c>
       <c r="E16">
-        <v>0.9498839907192576</v>
+        <v>0.9554524361948956</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16">
-        <v>0.9498839907192576</v>
+        <v>0.9554524361948956</v>
       </c>
       <c r="H16">
-        <v>0.05011600928074246</v>
+        <v>0.04454756380510441</v>
       </c>
       <c r="I16">
-        <v>1.618462905999877</v>
+        <v>1.510462211000004</v>
       </c>
       <c r="J16">
         <v>0.05</v>
       </c>
       <c r="M16">
-        <v>0.9566408444775192</v>
+        <v>0.9441629693790895</v>
       </c>
     </row>
   </sheetData>
@@ -3478,15 +3475,15 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3541,44 +3538,44 @@
         <v>0.95</v>
       </c>
       <c r="D5">
+        <v>0.965661252900232</v>
+      </c>
+      <c r="E5">
         <v>0.9661252900232019</v>
       </c>
-      <c r="E5">
-        <v>0.9670533642691416</v>
-      </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>0.9670533642691416</v>
+        <v>0.9661252900232019</v>
       </c>
       <c r="H5">
-        <v>0.03294663573085847</v>
+        <v>0.03387470997679815</v>
       </c>
       <c r="I5">
-        <v>1.596849406000274</v>
+        <v>1.484987718000014</v>
       </c>
       <c r="J5">
         <v>0.05</v>
       </c>
       <c r="M5">
-        <v>0.9723330633020304</v>
+        <v>0.9754523849408642</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -3586,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="B10">
-        <v>0.9649890590809628</v>
+        <v>0.962800875273523</v>
       </c>
       <c r="C10">
         <v>914</v>
@@ -3597,7 +3594,7 @@
         <v>1</v>
       </c>
       <c r="B11">
-        <v>0.9713656387665198</v>
+        <v>0.9669603524229075</v>
       </c>
       <c r="C11">
         <v>454</v>
@@ -3608,7 +3605,7 @@
         <v>2</v>
       </c>
       <c r="B12">
-        <v>0.9413407821229051</v>
+        <v>0.9441340782122905</v>
       </c>
       <c r="C12">
         <v>358</v>
@@ -3619,7 +3616,7 @@
         <v>3</v>
       </c>
       <c r="B13">
-        <v>0.9871794871794872</v>
+        <v>0.9935897435897436</v>
       </c>
       <c r="C13">
         <v>156</v>
@@ -3630,7 +3627,7 @@
         <v>4</v>
       </c>
       <c r="B14">
-        <v>0.9807692307692307</v>
+        <v>0.9903846153846154</v>
       </c>
       <c r="C14">
         <v>104</v>
@@ -3641,7 +3638,7 @@
         <v>5</v>
       </c>
       <c r="B15">
-        <v>0.9900990099009901</v>
+        <v>0.9702970297029703</v>
       </c>
       <c r="C15">
         <v>101</v>
@@ -3652,7 +3649,7 @@
         <v>6</v>
       </c>
       <c r="B16">
-        <v>0.9705882352941176</v>
+        <v>1</v>
       </c>
       <c r="C16">
         <v>68</v>
@@ -3660,18 +3657,18 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -3679,10 +3676,10 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21">
-        <v>34851</v>
+        <v>33185</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -3690,10 +3687,10 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C22">
-        <v>13411</v>
+        <v>13820</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -3701,10 +3698,10 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C23">
-        <v>13277</v>
+        <v>13067</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -3712,10 +3709,10 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24">
-        <v>4595</v>
+        <v>5965</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -3723,13 +3720,13 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C25">
-        <v>3254</v>
+        <v>3520</v>
       </c>
       <c r="J25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -3737,10 +3734,10 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C26">
-        <v>4925</v>
+        <v>4135</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -3748,10 +3745,10 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27">
-        <v>1442</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -3759,26 +3756,26 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C28">
-        <v>25555</v>
+        <v>25692</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -3786,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="B33">
-        <v>0.009562166328961785</v>
+        <v>0.0101018096014478</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -3797,7 +3794,7 @@
         <v>1</v>
       </c>
       <c r="B34">
-        <v>0.01317439070149451</v>
+        <v>0.0154701913740144</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -3808,7 +3805,7 @@
         <v>2</v>
       </c>
       <c r="B35">
-        <v>0.01462543088730883</v>
+        <v>0.01874896277291405</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -3819,7 +3816,7 @@
         <v>3</v>
       </c>
       <c r="B36">
-        <v>0.1077607163952938</v>
+        <v>0.4975534013607765</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -3830,7 +3827,7 @@
         <v>4</v>
       </c>
       <c r="B37">
-        <v>0.01146160186047673</v>
+        <v>0.01800418601859421</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -3841,7 +3838,7 @@
         <v>5</v>
       </c>
       <c r="B38">
-        <v>0.03614248412775134</v>
+        <v>0.02830171482285004</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -3852,7 +3849,7 @@
         <v>6</v>
       </c>
       <c r="B39">
-        <v>0.06007295387367062</v>
+        <v>0.2049890733469193</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -3860,12 +3857,12 @@
     </row>
     <row r="49" spans="10:10">
       <c r="J49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="10:10">
       <c r="J73" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -3881,15 +3878,15 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3944,22 +3941,22 @@
         <v>0.95</v>
       </c>
       <c r="D5">
-        <v>0.9503480278422274</v>
+        <v>0.9596287703016241</v>
       </c>
       <c r="E5">
-        <v>0.9503480278422274</v>
+        <v>0.9596287703016241</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>0.9503480278422274</v>
+        <v>0.9596287703016241</v>
       </c>
       <c r="H5">
-        <v>0.04965197215777262</v>
+        <v>0.04037122969837587</v>
       </c>
       <c r="I5">
-        <v>6.272273327000221</v>
+        <v>4.517080029999988</v>
       </c>
       <c r="J5">
         <v>0.05</v>
@@ -3968,23 +3965,23 @@
         <v>4</v>
       </c>
       <c r="M5">
-        <v>0.9459429557019886</v>
+        <v>0.9589286748347672</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4003,7 +4000,7 @@
         <v>1</v>
       </c>
       <c r="B11">
-        <v>0.8788546255506607</v>
+        <v>0.9030837004405287</v>
       </c>
       <c r="C11">
         <v>454</v>
@@ -4014,7 +4011,7 @@
         <v>2</v>
       </c>
       <c r="B12">
-        <v>0.9413407821229051</v>
+        <v>0.9553072625698324</v>
       </c>
       <c r="C12">
         <v>358</v>
@@ -4025,7 +4022,7 @@
         <v>3</v>
       </c>
       <c r="B13">
-        <v>0.9294871794871795</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="C13">
         <v>156</v>
@@ -4047,7 +4044,7 @@
         <v>5</v>
       </c>
       <c r="B15">
-        <v>0.9207920792079208</v>
+        <v>0.9504950495049505</v>
       </c>
       <c r="C15">
         <v>101</v>
@@ -4058,7 +4055,7 @@
         <v>6</v>
       </c>
       <c r="B16">
-        <v>0.9705882352941176</v>
+        <v>1</v>
       </c>
       <c r="C16">
         <v>68</v>
@@ -4066,15 +4063,15 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4117,7 +4114,7 @@
         <v>1</v>
       </c>
       <c r="J25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4138,15 +4135,15 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -4154,7 +4151,7 @@
         <v>0</v>
       </c>
       <c r="B32">
-        <v>0.06007295387367062</v>
+        <v>0.2049890733469193</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4162,7 +4159,7 @@
         <v>1</v>
       </c>
       <c r="B33">
-        <v>0.01482716486426461</v>
+        <v>0.02239621215250154</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4170,7 +4167,7 @@
         <v>2</v>
       </c>
       <c r="B34">
-        <v>0.01081179358714113</v>
+        <v>0.01207659658680627</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4178,20 +4175,20 @@
         <v>3</v>
       </c>
       <c r="B35">
-        <v>0.01523881177081687</v>
+        <v>0.02349835376845311</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4199,7 +4196,7 @@
         <v>0</v>
       </c>
       <c r="B40">
-        <v>0.9705882352941176</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4207,7 +4204,7 @@
         <v>1</v>
       </c>
       <c r="B41">
-        <v>0.9512195121951219</v>
+        <v>0.9577235772357724</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4215,7 +4212,7 @@
         <v>2</v>
       </c>
       <c r="B42">
-        <v>0.9511305616338439</v>
+        <v>0.9584548104956269</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4223,20 +4220,20 @@
         <v>3</v>
       </c>
       <c r="B43">
-        <v>0.9207920792079208</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -4244,7 +4241,7 @@
         <v>0</v>
       </c>
       <c r="B48">
-        <v>0.9890710382513661</v>
+        <v>0.9901531728665208</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -4252,10 +4249,10 @@
         <v>1</v>
       </c>
       <c r="B49">
-        <v>0.875</v>
+        <v>0.8951965065502183</v>
       </c>
       <c r="J49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -4263,7 +4260,7 @@
         <v>2</v>
       </c>
       <c r="B50">
-        <v>0.9519774011299436</v>
+        <v>0.9633802816901409</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -4271,7 +4268,7 @@
         <v>3</v>
       </c>
       <c r="B51">
-        <v>0.9235668789808917</v>
+        <v>0.9230769230769231</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -4287,7 +4284,7 @@
         <v>5</v>
       </c>
       <c r="B53">
-        <v>0.9207920792079208</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -4295,12 +4292,12 @@
         <v>6</v>
       </c>
       <c r="B54">
-        <v>0.9705882352941176</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="10:10">
       <c r="J73" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -4316,15 +4313,15 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4394,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.4127142659999663</v>
+        <v>0.7239199800000051</v>
       </c>
       <c r="J5">
         <v>0.05</v>
@@ -4403,23 +4400,23 @@
         <v>0.01</v>
       </c>
       <c r="M5">
-        <v>0.9974880798903145</v>
+        <v>0.9964726950317967</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4449,7 +4446,7 @@
         <v>2</v>
       </c>
       <c r="B12">
-        <v>0.9888268156424581</v>
+        <v>0.9916201117318436</v>
       </c>
       <c r="C12">
         <v>358</v>
@@ -4482,7 +4479,7 @@
         <v>5</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>0.9900990099009901</v>
       </c>
       <c r="C15">
         <v>101</v>
@@ -4501,18 +4498,18 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4539,15 +4536,15 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4602,44 +4599,44 @@
         <v>0.95</v>
       </c>
       <c r="D5">
-        <v>0.9475638051044084</v>
+        <v>0.9540603248259861</v>
       </c>
       <c r="E5">
-        <v>0.9498839907192576</v>
+        <v>0.9554524361948956</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>0.9498839907192576</v>
+        <v>0.9554524361948956</v>
       </c>
       <c r="H5">
-        <v>0.05011600928074246</v>
+        <v>0.04454756380510441</v>
       </c>
       <c r="I5">
-        <v>1.618462905999877</v>
+        <v>1.510462211000004</v>
       </c>
       <c r="J5">
         <v>0.05</v>
       </c>
       <c r="M5">
-        <v>0.9566408444775192</v>
+        <v>0.9441629693790895</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4647,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="B10">
-        <v>0.9310722100656456</v>
+        <v>0.9770240700218819</v>
       </c>
       <c r="C10">
         <v>914</v>
@@ -4658,7 +4655,7 @@
         <v>1</v>
       </c>
       <c r="B11">
-        <v>0.9537444933920705</v>
+        <v>0.9493392070484582</v>
       </c>
       <c r="C11">
         <v>454</v>
@@ -4669,7 +4666,7 @@
         <v>2</v>
       </c>
       <c r="B12">
-        <v>0.9664804469273743</v>
+        <v>0.9385474860335196</v>
       </c>
       <c r="C12">
         <v>358</v>
@@ -4680,7 +4677,7 @@
         <v>3</v>
       </c>
       <c r="B13">
-        <v>0.967948717948718</v>
+        <v>0.8525641025641025</v>
       </c>
       <c r="C13">
         <v>156</v>
@@ -4691,7 +4688,7 @@
         <v>4</v>
       </c>
       <c r="B14">
-        <v>0.9711538461538461</v>
+        <v>0.9903846153846154</v>
       </c>
       <c r="C14">
         <v>104</v>
@@ -4702,7 +4699,7 @@
         <v>5</v>
       </c>
       <c r="B15">
-        <v>0.9207920792079208</v>
+        <v>0.9306930693069307</v>
       </c>
       <c r="C15">
         <v>101</v>
@@ -4713,7 +4710,7 @@
         <v>6</v>
       </c>
       <c r="B16">
-        <v>0.9852941176470589</v>
+        <v>0.9705882352941176</v>
       </c>
       <c r="C16">
         <v>68</v>
@@ -4721,18 +4718,18 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4740,10 +4737,10 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21">
-        <v>36998</v>
+        <v>38219</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4751,10 +4748,10 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C22">
-        <v>16037</v>
+        <v>14049</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4762,10 +4759,10 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C23">
-        <v>15296</v>
+        <v>14934</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4773,10 +4770,10 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24">
-        <v>4231</v>
+        <v>4636</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4784,13 +4781,13 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C25">
-        <v>3334</v>
+        <v>3330</v>
       </c>
       <c r="J25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4798,10 +4795,10 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C26">
-        <v>4393</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -4809,10 +4806,10 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27">
-        <v>1801</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -4820,35 +4817,35 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C28">
-        <v>19220</v>
+        <v>20127</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33">
-        <v>0.04647925457013269</v>
+        <v>0.04500088007424996</v>
       </c>
     </row>
     <row r="49" spans="10:10">
       <c r="J49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="10:10">
       <c r="J73" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -4864,15 +4861,15 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4927,7 +4924,7 @@
         <v>0.95</v>
       </c>
       <c r="D5">
-        <v>0.954524361948956</v>
+        <v>0.9559164733178654</v>
       </c>
       <c r="E5">
         <v>0.9577726218097448</v>
@@ -4942,29 +4939,29 @@
         <v>0.04222737819025522</v>
       </c>
       <c r="I5">
-        <v>1.594293684000149</v>
+        <v>1.56471768900002</v>
       </c>
       <c r="J5">
         <v>0.05</v>
       </c>
       <c r="M5">
-        <v>0.9602821140459792</v>
+        <v>0.9610168565602223</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4972,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="B10">
-        <v>0.9540481400437637</v>
+        <v>0.9463894967177243</v>
       </c>
       <c r="C10">
         <v>914</v>
@@ -4983,7 +4980,7 @@
         <v>1</v>
       </c>
       <c r="B11">
-        <v>0.9537444933920705</v>
+        <v>0.9713656387665198</v>
       </c>
       <c r="C11">
         <v>454</v>
@@ -4994,7 +4991,7 @@
         <v>2</v>
       </c>
       <c r="B12">
-        <v>0.9385474860335196</v>
+        <v>0.9553072625698324</v>
       </c>
       <c r="C12">
         <v>358</v>
@@ -5005,7 +5002,7 @@
         <v>3</v>
       </c>
       <c r="B13">
-        <v>0.9935897435897436</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="C13">
         <v>156</v>
@@ -5016,7 +5013,7 @@
         <v>4</v>
       </c>
       <c r="B14">
-        <v>0.9711538461538461</v>
+        <v>0.9519230769230769</v>
       </c>
       <c r="C14">
         <v>104</v>
@@ -5027,7 +5024,7 @@
         <v>5</v>
       </c>
       <c r="B15">
-        <v>0.9108910891089109</v>
+        <v>0.9405940594059405</v>
       </c>
       <c r="C15">
         <v>101</v>
@@ -5046,18 +5043,18 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -5065,10 +5062,10 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21">
-        <v>37631</v>
+        <v>36815</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -5076,10 +5073,10 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C22">
-        <v>15915</v>
+        <v>15018</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -5087,10 +5084,10 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C23">
-        <v>14988</v>
+        <v>15121</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -5098,10 +5095,10 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24">
-        <v>6741</v>
+        <v>5308</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -5109,13 +5106,13 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C25">
-        <v>3355</v>
+        <v>2870</v>
       </c>
       <c r="J25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -5123,10 +5120,10 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C26">
-        <v>3602</v>
+        <v>4438</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -5134,10 +5131,10 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27">
-        <v>1967</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -5145,23 +5142,23 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C28">
-        <v>17111</v>
+        <v>19457</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -5169,7 +5166,7 @@
         <v>0</v>
       </c>
       <c r="B33">
-        <v>0.04670307833246812</v>
+        <v>0.04444869016833741</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -5177,7 +5174,7 @@
         <v>1</v>
       </c>
       <c r="B34">
-        <v>0.04576304545701848</v>
+        <v>0.04943422485252214</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -5185,7 +5182,7 @@
         <v>2</v>
       </c>
       <c r="B35">
-        <v>0.04532520444779753</v>
+        <v>0.04586620249475581</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -5193,7 +5190,7 @@
         <v>3</v>
       </c>
       <c r="B36">
-        <v>0.4124526080534733</v>
+        <v>0.05217212661280135</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -5201,7 +5198,7 @@
         <v>4</v>
       </c>
       <c r="B37">
-        <v>0.04862483127741457</v>
+        <v>0.03306250008262579</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -5209,7 +5206,7 @@
         <v>5</v>
       </c>
       <c r="B38">
-        <v>0.03740610842570624</v>
+        <v>0.05566573778639516</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -5217,17 +5214,17 @@
         <v>6</v>
       </c>
       <c r="B39">
-        <v>0.07079416156557738</v>
+        <v>0.1281712614714826</v>
       </c>
     </row>
     <row r="49" spans="10:10">
       <c r="J49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="10:10">
       <c r="J73" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -5243,15 +5240,15 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -5306,44 +5303,44 @@
         <v>0.95</v>
       </c>
       <c r="D5">
-        <v>0.9577726218097448</v>
+        <v>0.962877030162413</v>
       </c>
       <c r="E5">
-        <v>0.9610208816705337</v>
+        <v>0.9647331786542923</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>0.9610208816705337</v>
+        <v>0.9647331786542923</v>
       </c>
       <c r="H5">
-        <v>0.03897911832946636</v>
+        <v>0.03526682134570765</v>
       </c>
       <c r="I5">
-        <v>2.617920029000288</v>
+        <v>1.48396456200004</v>
       </c>
       <c r="J5">
         <v>0.05</v>
       </c>
       <c r="M5">
-        <v>0.9640907949938825</v>
+        <v>0.9697495534767266</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -5351,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="B10">
-        <v>0.9540481400437637</v>
+        <v>0.9562363238512035</v>
       </c>
       <c r="C10">
         <v>914</v>
@@ -5362,7 +5359,7 @@
         <v>1</v>
       </c>
       <c r="B11">
-        <v>0.9537444933920705</v>
+        <v>0.9713656387665198</v>
       </c>
       <c r="C11">
         <v>454</v>
@@ -5384,7 +5381,7 @@
         <v>3</v>
       </c>
       <c r="B13">
-        <v>0.9935897435897436</v>
+        <v>0.9743589743589743</v>
       </c>
       <c r="C13">
         <v>156</v>
@@ -5395,7 +5392,7 @@
         <v>4</v>
       </c>
       <c r="B14">
-        <v>0.9711538461538461</v>
+        <v>0.9903846153846154</v>
       </c>
       <c r="C14">
         <v>104</v>
@@ -5406,7 +5403,7 @@
         <v>5</v>
       </c>
       <c r="B15">
-        <v>0.9207920792079208</v>
+        <v>0.9405940594059405</v>
       </c>
       <c r="C15">
         <v>101</v>
@@ -5425,18 +5422,18 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -5444,10 +5441,10 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21">
-        <v>37716</v>
+        <v>37097</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -5455,10 +5452,10 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C22">
-        <v>15947</v>
+        <v>15023</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -5466,10 +5463,10 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C23">
-        <v>15117</v>
+        <v>15127</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -5477,10 +5474,10 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24">
-        <v>6741</v>
+        <v>5386</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -5488,13 +5485,13 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C25">
-        <v>3426</v>
+        <v>3641</v>
       </c>
       <c r="J25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -5502,10 +5499,10 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C26">
-        <v>3704</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -5513,10 +5510,10 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27">
-        <v>1967</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -5524,26 +5521,26 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C28">
-        <v>16692</v>
+        <v>18249</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -5551,7 +5548,7 @@
         <v>0</v>
       </c>
       <c r="B33">
-        <v>0.04673612593825061</v>
+        <v>0.04453517209265256</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -5562,7 +5559,7 @@
         <v>1</v>
       </c>
       <c r="B34">
-        <v>0.04592794979610337</v>
+        <v>0.04947591757448655</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -5573,7 +5570,7 @@
         <v>2</v>
       </c>
       <c r="B35">
-        <v>0.04561774006522523</v>
+        <v>0.04588505533406106</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -5584,7 +5581,7 @@
         <v>3</v>
       </c>
       <c r="B36">
-        <v>0.4124526080534733</v>
+        <v>0.05424874213193409</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -5595,7 +5592,7 @@
         <v>4</v>
       </c>
       <c r="B37">
-        <v>0.06080861442800145</v>
+        <v>0.09314523812105124</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -5606,7 +5603,7 @@
         <v>5</v>
       </c>
       <c r="B38">
-        <v>0.03822053732807984</v>
+        <v>0.0583277669193899</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -5617,7 +5614,7 @@
         <v>6</v>
       </c>
       <c r="B39">
-        <v>0.07079416156557738</v>
+        <v>0.1281712614714826</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -5625,12 +5622,12 @@
     </row>
     <row r="49" spans="10:10">
       <c r="J49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="10:10">
       <c r="J73" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -5646,15 +5643,15 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -5709,22 +5706,22 @@
         <v>0.95</v>
       </c>
       <c r="D5">
-        <v>0.951276102088167</v>
+        <v>0.9535962877030162</v>
       </c>
       <c r="E5">
-        <v>0.9535962877030162</v>
+        <v>0.9554524361948956</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>0.9535962877030162</v>
+        <v>0.9554524361948956</v>
       </c>
       <c r="H5">
-        <v>0.04640371229698376</v>
+        <v>0.04454756380510441</v>
       </c>
       <c r="I5">
-        <v>11.06494913400002</v>
+        <v>9.133538877000035</v>
       </c>
       <c r="J5">
         <v>0.05</v>
@@ -5733,23 +5730,23 @@
         <v>4</v>
       </c>
       <c r="M5">
-        <v>0.9585776484037607</v>
+        <v>0.9442845717138543</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -5757,7 +5754,7 @@
         <v>0</v>
       </c>
       <c r="B10">
-        <v>0.9398249452954048</v>
+        <v>0.9770240700218819</v>
       </c>
       <c r="C10">
         <v>914</v>
@@ -5768,7 +5765,7 @@
         <v>1</v>
       </c>
       <c r="B11">
-        <v>0.9537444933920705</v>
+        <v>0.9493392070484582</v>
       </c>
       <c r="C11">
         <v>454</v>
@@ -5779,7 +5776,7 @@
         <v>2</v>
       </c>
       <c r="B12">
-        <v>0.9664804469273743</v>
+        <v>0.9385474860335196</v>
       </c>
       <c r="C12">
         <v>358</v>
@@ -5790,7 +5787,7 @@
         <v>3</v>
       </c>
       <c r="B13">
-        <v>0.967948717948718</v>
+        <v>0.8525641025641025</v>
       </c>
       <c r="C13">
         <v>156</v>
@@ -5801,7 +5798,7 @@
         <v>4</v>
       </c>
       <c r="B14">
-        <v>0.9711538461538461</v>
+        <v>0.9519230769230769</v>
       </c>
       <c r="C14">
         <v>104</v>
@@ -5812,7 +5809,7 @@
         <v>5</v>
       </c>
       <c r="B15">
-        <v>0.9108910891089109</v>
+        <v>0.9405940594059405</v>
       </c>
       <c r="C15">
         <v>101</v>
@@ -5831,15 +5828,15 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -5882,7 +5879,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -5903,15 +5900,15 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -5919,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="B32">
-        <v>0.04862483127741457</v>
+        <v>0.03306250008262579</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -5927,7 +5924,7 @@
         <v>1</v>
       </c>
       <c r="B33">
-        <v>0.04658342562095774</v>
+        <v>0.04502466188358434</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -5935,7 +5932,7 @@
         <v>2</v>
       </c>
       <c r="B34">
-        <v>0.07079416156557738</v>
+        <v>0.1281712614714826</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -5943,20 +5940,20 @@
         <v>3</v>
       </c>
       <c r="B35">
-        <v>0.03740610842570624</v>
+        <v>0.05566573778639516</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -5964,7 +5961,7 @@
         <v>0</v>
       </c>
       <c r="B40">
-        <v>0.9619047619047619</v>
+        <v>0.9611650485436893</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -5972,7 +5969,7 @@
         <v>1</v>
       </c>
       <c r="B41">
-        <v>0.9517241379310345</v>
+        <v>0.9532908704883227</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -5988,20 +5985,20 @@
         <v>3</v>
       </c>
       <c r="B43">
-        <v>0.9484536082474226</v>
+        <v>0.9595959595959596</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -6009,7 +6006,7 @@
         <v>0</v>
       </c>
       <c r="B48">
-        <v>0.940854326396495</v>
+        <v>0.9791666666666666</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -6017,10 +6014,10 @@
         <v>1</v>
       </c>
       <c r="B49">
-        <v>0.956140350877193</v>
+        <v>0.9535398230088495</v>
       </c>
       <c r="J49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -6028,7 +6025,7 @@
         <v>2</v>
       </c>
       <c r="B50">
-        <v>0.9692737430167597</v>
+        <v>0.9441340782122905</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -6036,7 +6033,7 @@
         <v>3</v>
       </c>
       <c r="B51">
-        <v>0.9620253164556962</v>
+        <v>0.8271604938271605</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -6044,7 +6041,7 @@
         <v>4</v>
       </c>
       <c r="B52">
-        <v>0.9619047619047619</v>
+        <v>0.9611650485436893</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -6052,7 +6049,7 @@
         <v>5</v>
       </c>
       <c r="B53">
-        <v>0.9484536082474226</v>
+        <v>0.9595959595959596</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -6065,7 +6062,7 @@
     </row>
     <row r="73" spans="10:10">
       <c r="J73" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -6081,15 +6078,15 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -6144,7 +6141,7 @@
         <v>0.95</v>
       </c>
       <c r="D5">
-        <v>0.9925754060324826</v>
+        <v>0.9939675174013921</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -6159,7 +6156,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.4107737730000736</v>
+        <v>0.3752910420000148</v>
       </c>
       <c r="J5">
         <v>0.05</v>
@@ -6168,23 +6165,23 @@
         <v>0.01</v>
       </c>
       <c r="M5">
-        <v>0.9899444570242417</v>
+        <v>0.9925457202024014</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -6203,7 +6200,7 @@
         <v>1</v>
       </c>
       <c r="B11">
-        <v>0.9889867841409692</v>
+        <v>0.9933920704845814</v>
       </c>
       <c r="C11">
         <v>454</v>
@@ -6214,7 +6211,7 @@
         <v>2</v>
       </c>
       <c r="B12">
-        <v>0.9888268156424581</v>
+        <v>0.9860335195530726</v>
       </c>
       <c r="C12">
         <v>358</v>
@@ -6225,7 +6222,7 @@
         <v>3</v>
       </c>
       <c r="B13">
-        <v>0.9935897435897436</v>
+        <v>1</v>
       </c>
       <c r="C13">
         <v>156</v>
@@ -6236,7 +6233,7 @@
         <v>4</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>0.9903846153846154</v>
       </c>
       <c r="C14">
         <v>104</v>
@@ -6247,7 +6244,7 @@
         <v>5</v>
       </c>
       <c r="B15">
-        <v>0.9603960396039604</v>
+        <v>0.9801980198019802</v>
       </c>
       <c r="C15">
         <v>101</v>
@@ -6266,18 +6263,18 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6304,7 +6301,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -6359,31 +6356,31 @@
         <v>0.95</v>
       </c>
       <c r="D4">
-        <v>0.9568445475638051</v>
+        <v>0.9651972157772621</v>
       </c>
       <c r="E4">
-        <v>0.9568445475638051</v>
+        <v>0.9651972157772621</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>0.9568445475638051</v>
+        <v>0.9651972157772621</v>
       </c>
       <c r="H4">
-        <v>0.0431554524361949</v>
+        <v>0.03480278422273782</v>
       </c>
       <c r="I4" t="s">
         <v>13</v>
       </c>
       <c r="J4">
-        <v>0.947432035535824</v>
+        <v>0.9546374488073269</v>
       </c>
       <c r="L4">
         <v>4</v>
       </c>
       <c r="M4">
-        <v>0.9474320355358241</v>
+        <v>0.9546374488073269</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -6397,31 +6394,31 @@
         <v>0.95</v>
       </c>
       <c r="D5">
-        <v>0.9503480278422274</v>
+        <v>0.9596287703016241</v>
       </c>
       <c r="E5">
-        <v>0.9503480278422274</v>
+        <v>0.9596287703016241</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>0.9503480278422274</v>
+        <v>0.9596287703016241</v>
       </c>
       <c r="H5">
-        <v>0.04965197215777262</v>
+        <v>0.04037122969837587</v>
       </c>
       <c r="I5" t="s">
         <v>14</v>
       </c>
       <c r="J5">
-        <v>0.9459429557019885</v>
+        <v>0.9589286748347673</v>
       </c>
       <c r="L5">
         <v>4</v>
       </c>
       <c r="M5">
-        <v>0.9459429557019886</v>
+        <v>0.9589286748347672</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -6435,41 +6432,41 @@
         <v>0.95</v>
       </c>
       <c r="D6">
-        <v>0.951276102088167</v>
+        <v>0.9535962877030162</v>
       </c>
       <c r="E6">
-        <v>0.9535962877030162</v>
+        <v>0.9554524361948956</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6">
-        <v>0.9535962877030162</v>
+        <v>0.9554524361948956</v>
       </c>
       <c r="H6">
-        <v>0.04640371229698376</v>
+        <v>0.04454756380510441</v>
       </c>
       <c r="I6" t="s">
         <v>15</v>
       </c>
       <c r="J6">
-        <v>0.9585776484037607</v>
+        <v>0.9442845717138543</v>
       </c>
       <c r="L6">
         <v>4</v>
       </c>
       <c r="M6">
-        <v>0.9585776484037607</v>
+        <v>0.9442845717138543</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -6485,7 +6482,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -6558,13 +6555,13 @@
         <v>13</v>
       </c>
       <c r="J4">
-        <v>0.9992862943912584</v>
+        <v>0.9975844963536076</v>
       </c>
       <c r="K4">
         <v>0.01</v>
       </c>
       <c r="M4">
-        <v>0.9992862943912584</v>
+        <v>0.9975844963536076</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -6596,13 +6593,13 @@
         <v>14</v>
       </c>
       <c r="J5">
-        <v>0.9974880798903145</v>
+        <v>0.9964726950317967</v>
       </c>
       <c r="K5">
         <v>0.01</v>
       </c>
       <c r="M5">
-        <v>0.9974880798903145</v>
+        <v>0.9964726950317967</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -6616,7 +6613,7 @@
         <v>0.95</v>
       </c>
       <c r="D6">
-        <v>0.9925754060324826</v>
+        <v>0.9939675174013921</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -6634,23 +6631,23 @@
         <v>15</v>
       </c>
       <c r="J6">
-        <v>0.9899444570242417</v>
+        <v>0.9925457202024014</v>
       </c>
       <c r="K6">
         <v>0.01</v>
       </c>
       <c r="M6">
-        <v>0.9899444570242417</v>
+        <v>0.9925457202024014</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -6717,7 +6714,7 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -6813,7 +6810,7 @@
         <v>38</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -6828,15 +6825,15 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -6891,44 +6888,44 @@
         <v>0.95</v>
       </c>
       <c r="D5">
-        <v>0.9582366589327146</v>
+        <v>0.9577726218097448</v>
       </c>
       <c r="E5">
-        <v>0.9582366589327146</v>
+        <v>0.9577726218097448</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>0.9582366589327146</v>
+        <v>0.9577726218097448</v>
       </c>
       <c r="H5">
-        <v>0.04176334106728538</v>
+        <v>0.04222737819025522</v>
       </c>
       <c r="I5">
-        <v>2.624444249999669</v>
+        <v>1.631907137999974</v>
       </c>
       <c r="J5">
         <v>0.05</v>
       </c>
       <c r="M5">
-        <v>0.9299937688165701</v>
+        <v>0.9154465450525774</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -6947,7 +6944,7 @@
         <v>1</v>
       </c>
       <c r="B11">
-        <v>0.947136563876652</v>
+        <v>0.9647577092511013</v>
       </c>
       <c r="C11">
         <v>454</v>
@@ -6958,7 +6955,7 @@
         <v>2</v>
       </c>
       <c r="B12">
-        <v>0.9553072625698324</v>
+        <v>0.9497206703910615</v>
       </c>
       <c r="C12">
         <v>358</v>
@@ -6969,7 +6966,7 @@
         <v>3</v>
       </c>
       <c r="B13">
-        <v>0.9038461538461539</v>
+        <v>0.8974358974358975</v>
       </c>
       <c r="C13">
         <v>156</v>
@@ -6991,7 +6988,7 @@
         <v>5</v>
       </c>
       <c r="B15">
-        <v>0.8514851485148515</v>
+        <v>0.8910891089108911</v>
       </c>
       <c r="C15">
         <v>101</v>
@@ -7002,7 +6999,7 @@
         <v>6</v>
       </c>
       <c r="B16">
-        <v>0.8823529411764706</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="C16">
         <v>68</v>
@@ -7010,18 +7007,18 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -7029,10 +7026,10 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21">
-        <v>35620</v>
+        <v>36107</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -7040,10 +7037,10 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C22">
-        <v>12054</v>
+        <v>12076</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -7051,10 +7048,10 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C23">
-        <v>14686</v>
+        <v>12793</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -7062,10 +7059,10 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24">
-        <v>3571</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -7073,13 +7070,13 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C25">
-        <v>3898</v>
+        <v>3074</v>
       </c>
       <c r="J25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -7087,10 +7084,10 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C26">
-        <v>3086</v>
+        <v>3883</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -7098,10 +7095,10 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27">
-        <v>1462</v>
+        <v>808</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -7109,35 +7106,35 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C28">
-        <v>26933</v>
+        <v>29928</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33">
-        <v>0.001935439826539764</v>
+        <v>0.0003268775013226533</v>
       </c>
     </row>
     <row r="49" spans="10:10">
       <c r="J49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="10:10">
       <c r="J73" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -7153,15 +7150,15 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -7216,44 +7213,44 @@
         <v>0.95</v>
       </c>
       <c r="D5">
-        <v>0.9642691415313225</v>
+        <v>0.9647331786542923</v>
       </c>
       <c r="E5">
-        <v>0.9642691415313225</v>
+        <v>0.9647331786542923</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>0.9642691415313225</v>
+        <v>0.9647331786542923</v>
       </c>
       <c r="H5">
-        <v>0.0357308584686775</v>
+        <v>0.03526682134570765</v>
       </c>
       <c r="I5">
-        <v>2.050202063000143</v>
+        <v>1.519001585000012</v>
       </c>
       <c r="J5">
         <v>0.05</v>
       </c>
       <c r="M5">
-        <v>0.9595146470000567</v>
+        <v>0.968021548786501</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -7261,7 +7258,7 @@
         <v>0</v>
       </c>
       <c r="B10">
-        <v>0.9584245076586433</v>
+        <v>0.962800875273523</v>
       </c>
       <c r="C10">
         <v>914</v>
@@ -7272,7 +7269,7 @@
         <v>1</v>
       </c>
       <c r="B11">
-        <v>0.9801762114537445</v>
+        <v>0.9669603524229075</v>
       </c>
       <c r="C11">
         <v>454</v>
@@ -7283,7 +7280,7 @@
         <v>2</v>
       </c>
       <c r="B12">
-        <v>0.9608938547486033</v>
+        <v>0.9581005586592178</v>
       </c>
       <c r="C12">
         <v>358</v>
@@ -7294,7 +7291,7 @@
         <v>3</v>
       </c>
       <c r="B13">
-        <v>0.9743589743589743</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="C13">
         <v>156</v>
@@ -7305,7 +7302,7 @@
         <v>4</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>0.9807692307692307</v>
       </c>
       <c r="C14">
         <v>104</v>
@@ -7316,7 +7313,7 @@
         <v>5</v>
       </c>
       <c r="B15">
-        <v>0.9603960396039604</v>
+        <v>0.9900990099009901</v>
       </c>
       <c r="C15">
         <v>101</v>
@@ -7327,7 +7324,7 @@
         <v>6</v>
       </c>
       <c r="B16">
-        <v>0.8823529411764706</v>
+        <v>0.9558823529411765</v>
       </c>
       <c r="C16">
         <v>68</v>
@@ -7335,18 +7332,18 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -7354,10 +7351,10 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21">
-        <v>31952</v>
+        <v>33166</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -7365,10 +7362,10 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C22">
-        <v>13676</v>
+        <v>12121</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -7376,10 +7373,10 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C23">
-        <v>14805</v>
+        <v>12967</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -7387,10 +7384,10 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24">
-        <v>4341</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -7398,13 +7395,13 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C25">
-        <v>4588</v>
+        <v>3418</v>
       </c>
       <c r="J25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -7412,10 +7409,10 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C26">
-        <v>3566</v>
+        <v>4677</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -7423,10 +7420,10 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27">
-        <v>1523</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -7434,23 +7431,23 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C28">
-        <v>26859</v>
+        <v>30246</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -7458,7 +7455,7 @@
         <v>0</v>
       </c>
       <c r="B33">
-        <v>4.05952860115244E-05</v>
+        <v>1.177074451852445E-05</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -7466,7 +7463,7 @@
         <v>1</v>
       </c>
       <c r="B34">
-        <v>0.01036355542998668</v>
+        <v>0.0003441673254563904</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -7474,7 +7471,7 @@
         <v>2</v>
       </c>
       <c r="B35">
-        <v>0.002240963613344693</v>
+        <v>0.000413795471140288</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -7482,7 +7479,7 @@
         <v>3</v>
       </c>
       <c r="B36">
-        <v>0.007906291212185779</v>
+        <v>0.001056294925310231</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -7490,7 +7487,7 @@
         <v>4</v>
       </c>
       <c r="B37">
-        <v>0.05387729061468449</v>
+        <v>0.002719837499994049</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -7498,7 +7495,7 @@
         <v>5</v>
       </c>
       <c r="B38">
-        <v>0.005477072210675504</v>
+        <v>0.002628571777141708</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -7506,17 +7503,17 @@
         <v>6</v>
       </c>
       <c r="B39">
-        <v>0.002987885844663807</v>
+        <v>0.02274074562204165</v>
       </c>
     </row>
     <row r="49" spans="10:10">
       <c r="J49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="10:10">
       <c r="J73" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -7532,15 +7529,15 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -7595,44 +7592,44 @@
         <v>0.95</v>
       </c>
       <c r="D5">
-        <v>0.9670533642691416</v>
+        <v>0.9716937354988399</v>
       </c>
       <c r="E5">
-        <v>0.9670533642691416</v>
+        <v>0.9716937354988399</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>0.9670533642691416</v>
+        <v>0.9716937354988399</v>
       </c>
       <c r="H5">
-        <v>0.03294663573085847</v>
+        <v>0.02830626450116009</v>
       </c>
       <c r="I5">
-        <v>1.603470881000248</v>
+        <v>1.489061632000016</v>
       </c>
       <c r="J5">
         <v>0.05</v>
       </c>
       <c r="M5">
-        <v>0.961613000054715</v>
+        <v>0.974236360209212</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -7640,7 +7637,7 @@
         <v>0</v>
       </c>
       <c r="B10">
-        <v>0.9617067833698031</v>
+        <v>0.9682713347921226</v>
       </c>
       <c r="C10">
         <v>914</v>
@@ -7651,7 +7648,7 @@
         <v>1</v>
       </c>
       <c r="B11">
-        <v>0.9823788546255506</v>
+        <v>0.9801762114537445</v>
       </c>
       <c r="C11">
         <v>454</v>
@@ -7673,7 +7670,7 @@
         <v>3</v>
       </c>
       <c r="B13">
-        <v>0.9807692307692307</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="C13">
         <v>156</v>
@@ -7695,7 +7692,7 @@
         <v>5</v>
       </c>
       <c r="B15">
-        <v>0.9603960396039604</v>
+        <v>0.9900990099009901</v>
       </c>
       <c r="C15">
         <v>101</v>
@@ -7706,7 +7703,7 @@
         <v>6</v>
       </c>
       <c r="B16">
-        <v>0.8823529411764706</v>
+        <v>0.9558823529411765</v>
       </c>
       <c r="C16">
         <v>68</v>
@@ -7714,18 +7711,18 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -7733,10 +7730,10 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21">
-        <v>32380</v>
+        <v>33588</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -7744,10 +7741,10 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C22">
-        <v>14274</v>
+        <v>12467</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -7755,10 +7752,10 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C23">
-        <v>15007</v>
+        <v>13159</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -7766,10 +7763,10 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24">
-        <v>4389</v>
+        <v>3216</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -7777,13 +7774,13 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C25">
-        <v>4691</v>
+        <v>3709</v>
       </c>
       <c r="J25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -7791,10 +7788,10 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C26">
-        <v>3691</v>
+        <v>4860</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -7802,10 +7799,10 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27">
-        <v>1523</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -7813,26 +7810,26 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C28">
-        <v>25355</v>
+        <v>28726</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -7840,7 +7837,7 @@
         <v>0</v>
       </c>
       <c r="B33">
-        <v>6.212310533126875E-05</v>
+        <v>1.786882404408718E-05</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -7851,7 +7848,7 @@
         <v>1</v>
       </c>
       <c r="B34">
-        <v>0.01861026886729988</v>
+        <v>0.0005481916974863221</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -7862,7 +7859,7 @@
         <v>2</v>
       </c>
       <c r="B35">
-        <v>0.002796217983783489</v>
+        <v>0.0005578971724876647</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -7873,7 +7870,7 @@
         <v>3</v>
       </c>
       <c r="B36">
-        <v>0.008879538294625955</v>
+        <v>0.001294168981404997</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -7884,7 +7881,7 @@
         <v>4</v>
       </c>
       <c r="B37">
-        <v>0.07736754522853051</v>
+        <v>0.01796032248781143</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -7895,7 +7892,7 @@
         <v>5</v>
       </c>
       <c r="B38">
-        <v>0.007397387674645817</v>
+        <v>0.004173764604947117</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -7906,7 +7903,7 @@
         <v>6</v>
       </c>
       <c r="B39">
-        <v>0.002987885844663807</v>
+        <v>0.02274074562204165</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -7914,12 +7911,12 @@
     </row>
     <row r="49" spans="10:10">
       <c r="J49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="10:10">
       <c r="J73" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -7935,15 +7932,15 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -7998,22 +7995,22 @@
         <v>0.95</v>
       </c>
       <c r="D5">
-        <v>0.9568445475638051</v>
+        <v>0.9651972157772621</v>
       </c>
       <c r="E5">
-        <v>0.9568445475638051</v>
+        <v>0.9651972157772621</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>0.9568445475638051</v>
+        <v>0.9651972157772621</v>
       </c>
       <c r="H5">
-        <v>0.0431554524361949</v>
+        <v>0.03480278422273782</v>
       </c>
       <c r="I5">
-        <v>2.497895874999813</v>
+        <v>2.407274647999998</v>
       </c>
       <c r="J5">
         <v>0.05</v>
@@ -8022,23 +8019,23 @@
         <v>4</v>
       </c>
       <c r="M5">
-        <v>0.9474320355358241</v>
+        <v>0.9546374488073269</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -8046,7 +8043,7 @@
         <v>0</v>
       </c>
       <c r="B10">
-        <v>0.9584245076586433</v>
+        <v>0.962800875273523</v>
       </c>
       <c r="C10">
         <v>914</v>
@@ -8057,7 +8054,7 @@
         <v>1</v>
       </c>
       <c r="B11">
-        <v>0.960352422907489</v>
+        <v>0.9713656387665198</v>
       </c>
       <c r="C11">
         <v>454</v>
@@ -8068,7 +8065,7 @@
         <v>2</v>
       </c>
       <c r="B12">
-        <v>0.9664804469273743</v>
+        <v>0.9776536312849162</v>
       </c>
       <c r="C12">
         <v>358</v>
@@ -8079,7 +8076,7 @@
         <v>3</v>
       </c>
       <c r="B13">
-        <v>0.9487179487179487</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="C13">
         <v>156</v>
@@ -8090,7 +8087,7 @@
         <v>4</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>0.9807692307692307</v>
       </c>
       <c r="C14">
         <v>104</v>
@@ -8101,7 +8098,7 @@
         <v>5</v>
       </c>
       <c r="B15">
-        <v>0.900990099009901</v>
+        <v>0.9900990099009901</v>
       </c>
       <c r="C15">
         <v>101</v>
@@ -8112,7 +8109,7 @@
         <v>6</v>
       </c>
       <c r="B16">
-        <v>0.8970588235294118</v>
+        <v>0.8382352941176471</v>
       </c>
       <c r="C16">
         <v>68</v>
@@ -8120,15 +8117,15 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -8136,7 +8133,7 @@
         <v>0</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -8144,7 +8141,7 @@
         <v>1</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -8152,7 +8149,7 @@
         <v>2</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -8160,7 +8157,7 @@
         <v>3</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -8168,10 +8165,10 @@
         <v>4</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -8179,7 +8176,7 @@
         <v>5</v>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -8187,20 +8184,20 @@
         <v>6</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -8208,7 +8205,7 @@
         <v>0</v>
       </c>
       <c r="B32">
-        <v>0.004472456484343912</v>
+        <v>1.177074451852445E-05</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -8216,7 +8213,7 @@
         <v>1</v>
       </c>
       <c r="B33">
-        <v>0.05387729061468449</v>
+        <v>0.002628571777141708</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -8224,7 +8221,7 @@
         <v>2</v>
       </c>
       <c r="B34">
-        <v>4.05952860115244E-05</v>
+        <v>0.001147811433088508</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -8232,20 +8229,20 @@
         <v>3</v>
       </c>
       <c r="B35">
-        <v>0.003831536601078822</v>
+        <v>0.0004918037236156803</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -8253,7 +8250,7 @@
         <v>0</v>
       </c>
       <c r="B40">
-        <v>0.9627329192546584</v>
+        <v>0.9617486338797814</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -8261,7 +8258,7 @@
         <v>1</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>0.9803921568627451</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -8269,7 +8266,7 @@
         <v>2</v>
       </c>
       <c r="B42">
-        <v>0.9573770491803278</v>
+        <v>0.9586919104991394</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -8277,20 +8274,20 @@
         <v>3</v>
       </c>
       <c r="B43">
-        <v>0.8941176470588236</v>
+        <v>0.9748653500897666</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -8298,7 +8295,7 @@
         <v>0</v>
       </c>
       <c r="B48">
-        <v>0.9573770491803278</v>
+        <v>0.9617486338797814</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -8306,10 +8303,10 @@
         <v>1</v>
       </c>
       <c r="B49">
-        <v>0.9624724061810155</v>
+        <v>0.9735099337748344</v>
       </c>
       <c r="J49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -8317,7 +8314,7 @@
         <v>2</v>
       </c>
       <c r="B50">
-        <v>0.969187675070028</v>
+        <v>0.9776536312849162</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -8325,7 +8322,7 @@
         <v>3</v>
       </c>
       <c r="B51">
-        <v>0.9487179487179487</v>
+        <v>0.9615384615384616</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -8333,7 +8330,7 @@
         <v>4</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>0.9807692307692307</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -8341,7 +8338,7 @@
         <v>5</v>
       </c>
       <c r="B53">
-        <v>0.8921568627450981</v>
+        <v>0.9803921568627451</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -8349,12 +8346,12 @@
         <v>6</v>
       </c>
       <c r="B54">
-        <v>0.8970588235294118</v>
+        <v>0.8507462686567164</v>
       </c>
     </row>
     <row r="73" spans="10:10">
       <c r="J73" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -8370,15 +8367,15 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8448,7 +8445,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.3968220050001037</v>
+        <v>0.3762310320000211</v>
       </c>
       <c r="J5">
         <v>0.05</v>
@@ -8457,23 +8454,23 @@
         <v>0.01</v>
       </c>
       <c r="M5">
-        <v>0.9992862943912584</v>
+        <v>0.9975844963536076</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -8503,7 +8500,7 @@
         <v>2</v>
       </c>
       <c r="B12">
-        <v>0.9972067039106145</v>
+        <v>1</v>
       </c>
       <c r="C12">
         <v>358</v>
@@ -8547,7 +8544,7 @@
         <v>6</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>0.9852941176470589</v>
       </c>
       <c r="C16">
         <v>68</v>
@@ -8555,18 +8552,18 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8593,15 +8590,15 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8656,44 +8653,44 @@
         <v>0.95</v>
       </c>
       <c r="D5">
-        <v>0.9522041763341067</v>
+        <v>0.9498839907192576</v>
       </c>
       <c r="E5">
-        <v>0.9522041763341067</v>
+        <v>0.9498839907192576</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>0.9522041763341067</v>
+        <v>0.9498839907192576</v>
       </c>
       <c r="H5">
-        <v>0.04779582366589327</v>
+        <v>0.05011600928074246</v>
       </c>
       <c r="I5">
-        <v>1.608272338000006</v>
+        <v>1.53999763600001</v>
       </c>
       <c r="J5">
         <v>0.05</v>
       </c>
       <c r="M5">
-        <v>0.9232578513467463</v>
+        <v>0.9226677227224513</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -8712,7 +8709,7 @@
         <v>1</v>
       </c>
       <c r="B11">
-        <v>0.9581497797356828</v>
+        <v>0.9669603524229075</v>
       </c>
       <c r="C11">
         <v>454</v>
@@ -8723,7 +8720,7 @@
         <v>2</v>
       </c>
       <c r="B12">
-        <v>0.8938547486033519</v>
+        <v>0.8659217877094972</v>
       </c>
       <c r="C12">
         <v>358</v>
@@ -8745,7 +8742,7 @@
         <v>4</v>
       </c>
       <c r="B14">
-        <v>0.9903846153846154</v>
+        <v>0.9807692307692307</v>
       </c>
       <c r="C14">
         <v>104</v>
@@ -8756,7 +8753,7 @@
         <v>5</v>
       </c>
       <c r="B15">
-        <v>0.8712871287128713</v>
+        <v>0.8811881188118812</v>
       </c>
       <c r="C15">
         <v>101</v>
@@ -8767,7 +8764,7 @@
         <v>6</v>
       </c>
       <c r="B16">
-        <v>0.8529411764705882</v>
+        <v>0.8676470588235294</v>
       </c>
       <c r="C16">
         <v>68</v>
@@ -8775,18 +8772,18 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -8794,10 +8791,10 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21">
-        <v>39442</v>
+        <v>38134</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -8805,10 +8802,10 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C22">
-        <v>12564</v>
+        <v>13439</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -8816,10 +8813,10 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C23">
-        <v>12091</v>
+        <v>11320</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -8827,10 +8824,10 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24">
-        <v>2469</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -8838,13 +8835,13 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C25">
-        <v>3367</v>
+        <v>3285</v>
       </c>
       <c r="J25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -8852,10 +8849,10 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C26">
-        <v>2924</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -8863,10 +8860,10 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27">
-        <v>909</v>
+        <v>989</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -8874,35 +8871,35 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C28">
-        <v>27544</v>
+        <v>28726</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33">
-        <v>0.01221987971173688</v>
+        <v>0.01476347385333199</v>
       </c>
     </row>
     <row r="49" spans="10:10">
       <c r="J49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="10:10">
       <c r="J73" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -8918,15 +8915,15 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8981,44 +8978,44 @@
         <v>0.95</v>
       </c>
       <c r="D5">
-        <v>0.9610208816705337</v>
+        <v>0.9619489559164733</v>
       </c>
       <c r="E5">
-        <v>0.9614849187935035</v>
+        <v>0.9624129930394432</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>0.9614849187935035</v>
+        <v>0.9624129930394432</v>
       </c>
       <c r="H5">
-        <v>0.03851508120649652</v>
+        <v>0.03758700696055684</v>
       </c>
       <c r="I5">
-        <v>1.587323905000176</v>
+        <v>1.50927251600001</v>
       </c>
       <c r="J5">
         <v>0.05</v>
       </c>
       <c r="M5">
-        <v>0.9605619388469139</v>
+        <v>0.9709575072012449</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -9026,7 +9023,7 @@
         <v>0</v>
       </c>
       <c r="B10">
-        <v>0.9638949671772429</v>
+        <v>0.9595185995623632</v>
       </c>
       <c r="C10">
         <v>914</v>
@@ -9037,7 +9034,7 @@
         <v>1</v>
       </c>
       <c r="B11">
-        <v>0.9713656387665198</v>
+        <v>0.9669603524229075</v>
       </c>
       <c r="C11">
         <v>454</v>
@@ -9059,7 +9056,7 @@
         <v>3</v>
       </c>
       <c r="B13">
-        <v>0.9807692307692307</v>
+        <v>0.9935897435897436</v>
       </c>
       <c r="C13">
         <v>156</v>
@@ -9070,7 +9067,7 @@
         <v>4</v>
       </c>
       <c r="B14">
-        <v>0.9807692307692307</v>
+        <v>0.9903846153846154</v>
       </c>
       <c r="C14">
         <v>104</v>
@@ -9081,7 +9078,7 @@
         <v>5</v>
       </c>
       <c r="B15">
-        <v>0.9207920792079208</v>
+        <v>0.9504950495049505</v>
       </c>
       <c r="C15">
         <v>101</v>
@@ -9092,7 +9089,7 @@
         <v>6</v>
       </c>
       <c r="B16">
-        <v>0.9705882352941176</v>
+        <v>1</v>
       </c>
       <c r="C16">
         <v>68</v>
@@ -9100,18 +9097,18 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -9119,10 +9116,10 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21">
-        <v>34430</v>
+        <v>32702</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -9130,10 +9127,10 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C22">
-        <v>13345</v>
+        <v>13663</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -9141,10 +9138,10 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C23">
-        <v>13076</v>
+        <v>13007</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -9152,10 +9149,10 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24">
-        <v>4369</v>
+        <v>5965</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -9163,13 +9160,13 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C25">
-        <v>3107</v>
+        <v>3434</v>
       </c>
       <c r="J25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -9177,10 +9174,10 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C26">
-        <v>3523</v>
+        <v>3789</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -9188,10 +9185,10 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27">
-        <v>1442</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -9199,23 +9196,23 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C28">
-        <v>28018</v>
+        <v>26824</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -9223,7 +9220,7 @@
         <v>0</v>
       </c>
       <c r="B33">
-        <v>0.009531360058089855</v>
+        <v>0.0100415198033954</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -9231,7 +9228,7 @@
         <v>1</v>
       </c>
       <c r="B34">
-        <v>0.0130969524465584</v>
+        <v>0.01516221849028665</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -9239,7 +9236,7 @@
         <v>2</v>
       </c>
       <c r="B35">
-        <v>0.01409070512635757</v>
+        <v>0.01851797770245556</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -9247,7 +9244,7 @@
         <v>3</v>
       </c>
       <c r="B36">
-        <v>0.07894353739801507</v>
+        <v>0.4975534013607765</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -9255,7 +9252,7 @@
         <v>4</v>
       </c>
       <c r="B37">
-        <v>0.01084434831961401</v>
+        <v>0.0163959264755249</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -9263,7 +9260,7 @@
         <v>5</v>
       </c>
       <c r="B38">
-        <v>0.01523881177081687</v>
+        <v>0.02349835376845311</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -9271,17 +9268,17 @@
         <v>6</v>
       </c>
       <c r="B39">
-        <v>0.06007295387367062</v>
+        <v>0.2049890733469193</v>
       </c>
     </row>
     <row r="49" spans="10:10">
       <c r="J49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="10:10">
       <c r="J73" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
